--- a/out/MLP-mamba2_repeat_1_000001.xlsx
+++ b/out/MLP-mamba2_repeat_1_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.703898596494605</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.303898596494605</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.703898596494605</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.278093362574747</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.278093362574747</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.278093362574747</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002881716957349563</v>
+        <v>-0.0002796468697477831</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1240782583563696</v>
+        <v>0.1204077157953481</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2484878637499386</v>
+        <v>0.2411369829202602</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4793807585995274</v>
+        <v>0.465199511507898</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.083488208863407</v>
+        <v>1.05143598989441</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1474596996037666</v>
+        <v>0.143097468502398</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8984210130457422</v>
+        <v>0.8718435312277609</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02992087651506676</v>
+        <v>0.02903554081093438</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8105713602284266</v>
+        <v>0.7865926762108219</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02591245104400824</v>
+        <v>0.02514606876553335</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8324430243573389</v>
+        <v>0.8078174766516071</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01266800922329269</v>
+        <v>0.01229369214970042</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.703898596494605</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8318331510979056</v>
+        <v>0.8072256395301388</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006043957595353484</v>
+        <v>0.005864887603576754</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8312381435386127</v>
+        <v>0.8066480972840986</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002515227089165115</v>
+        <v>0.002440627921957665</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.303898596494605</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8302170264545498</v>
+        <v>0.8056570574452896</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001741292581929114</v>
+        <v>0.001689590592097364</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8311828750251276</v>
+        <v>0.8065941687491776</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007243329107880698</v>
+        <v>0.0007024271519834811</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.303898596494605</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8308875774168473</v>
+        <v>0.8063074627895002</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003731851318866753</v>
+        <v>0.0003618262144978529</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8309088546704713</v>
+        <v>0.8063279747102741</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001435365364654158</v>
+        <v>0.0001393376237738139</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8308222975942267</v>
+        <v>0.8062437231344178</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.574128984836033e-05</v>
+        <v>7.345075680301679e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8308306512515021</v>
+        <v>0.8062516993213185</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.509169298536786e-05</v>
+        <v>3.39623495209913e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8308244287618962</v>
+        <v>0.8062455112680394</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.364889654592446e-05</v>
+        <v>1.311607093032661e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8308171216511042</v>
+        <v>0.8062382691637165</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>2.839921505579082e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8308095182872405</v>
+        <v>0.8062307386913286</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8308036475609364</v>
+        <v>0.8062248679650245</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8307977827649352</v>
+        <v>0.8062190031690232</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.830792103588227</v>
+        <v>0.8062133239923149</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8307872222899776</v>
+        <v>0.8062084426940657</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8307823010884298</v>
+        <v>0.8062035214925178</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8307822931173353</v>
+        <v>0.8062035135214233</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8307824525392244</v>
+        <v>0.8062036729433124</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.806203577290179</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8307827076142472</v>
+        <v>0.8062039280183353</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8307824605103189</v>
+        <v>0.8062036809144069</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8307824206548466</v>
+        <v>0.8062036410589346</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.806203577290179</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8307824286259411</v>
+        <v>0.8062036490300291</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.806203577290179</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8307824605103189</v>
+        <v>0.8062036809144069</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8307825561634525</v>
+        <v>0.8062037765675406</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8307824923946967</v>
+        <v>0.8062037127987847</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8307824525392244</v>
+        <v>0.8062036729433124</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8307824286259411</v>
+        <v>0.8062036490300291</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8307821815220129</v>
+        <v>0.806203401926101</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8307821018110682</v>
+        <v>0.8062033222151561</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8307821496376349</v>
+        <v>0.8062033700417229</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.830782269204052</v>
+        <v>0.8062034896081399</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8307822532618631</v>
+        <v>0.806203473665951</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.830782269204052</v>
+        <v>0.8062034896081399</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8307822532618631</v>
+        <v>0.806203473665951</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8307823090595242</v>
+        <v>0.8062035294636123</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8307823090595242</v>
+        <v>0.8062035294636123</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.703898596494605</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8307823090595242</v>
+        <v>0.8062035294636123</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8307824605103189</v>
+        <v>0.8062036809144069</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8307826757298694</v>
+        <v>0.8062038961339574</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8307825880478303</v>
+        <v>0.8062038084519184</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.303898596494605</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8307825402212636</v>
+        <v>0.8062037606253517</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8307825880478303</v>
+        <v>0.8062038084519184</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8307824047126576</v>
+        <v>0.8062036251167457</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8307824126837521</v>
+        <v>0.8062036330878402</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.703898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8307824206548466</v>
+        <v>0.8062036410589346</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8307824286259411</v>
+        <v>0.8062036490300291</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8307824286259411</v>
+        <v>0.8062036490300291</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.703898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8307824684814133</v>
+        <v>0.8062036888855013</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8307825322501692</v>
+        <v>0.8062037526542573</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8307826438454916</v>
+        <v>0.8062038642495796</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8307826916720583</v>
+        <v>0.8062039120761464</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8307826518165861</v>
+        <v>0.806203872220674</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.703898596494605</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8307825800767359</v>
+        <v>0.806203800480824</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8307826996431528</v>
+        <v>0.8062039200472408</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8307825402212636</v>
+        <v>0.8062037606253517</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8307823090595242</v>
+        <v>0.8062035294636123</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8307822612329575</v>
+        <v>0.8062034816370455</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.278093362574747</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8307822931173353</v>
+        <v>0.8062035135214233</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.278093362574747</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.806203577290179</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.806203577290179</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8307822771751464</v>
+        <v>0.8062034975792344</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8307821576087293</v>
+        <v>0.8062033780128174</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8307821177532571</v>
+        <v>0.8062033381573451</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8307822612329575</v>
+        <v>0.8062034816370455</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6780933625747476</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8307823967415632</v>
+        <v>0.8062036171456513</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8307823807993743</v>
+        <v>0.8062036012034623</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.806203577290179</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8307823170306187</v>
+        <v>0.8062035374347067</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8307822134063907</v>
+        <v>0.8062034338104788</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.303898596494605</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8307820938399737</v>
+        <v>0.8062033142440617</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8307822134063907</v>
+        <v>0.8062034338104788</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8307822612329575</v>
+        <v>0.8062034816370455</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.806203577290179</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8307822373196742</v>
+        <v>0.8062034577237621</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.303898596494605</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8307822452907686</v>
+        <v>0.8062034656948566</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000001.xlsx
+++ b/out/MLP-mamba2_repeat_1_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.3117046516296653</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.02909442940683214</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931679</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683214</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.02909442940683214</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931679</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.5106925914798269</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.029094429406832</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.029094429406832</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.029094429406832</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.029094429406832</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002881716957349563</v>
+        <v>-0.0002252983685754007</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1240782583563696</v>
+        <v>0.09700682914012623</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2484878637499386</v>
+        <v>0.1942727588303261</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4793807585995274</v>
+        <v>0.3747886833462462</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.083488208863407</v>
+        <v>0.8470928104491264</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1474596996037666</v>
+        <v>0.1152870999546297</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.029094429406832</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8984210130457422</v>
+        <v>0.7024032384782659</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02992087651506676</v>
+        <v>0.02339261016103038</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8105713602284266</v>
+        <v>0.633720397376849</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02591245104400824</v>
+        <v>0.02025939782276486</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683193</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8324430243573389</v>
+        <v>0.650820308430311</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01266800922329269</v>
+        <v>0.009904359801443241</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.02909442940683196</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8318331510979056</v>
+        <v>0.650343497418331</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006043957595353484</v>
+        <v>0.004724318663416763</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.6525037326661629</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8312381435386127</v>
+        <v>0.6498772306750361</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002515227089165115</v>
+        <v>0.001965197408560933</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.02909442940683196</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8302170264545498</v>
+        <v>0.649077877160457</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001741292581929114</v>
+        <v>0.00136008686585621</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8311828750251276</v>
+        <v>0.6498318420035015</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007243329107880698</v>
+        <v>0.0005651940159429698</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.02909442940683196</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8308875774168473</v>
+        <v>0.6495998867178759</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003731851318866753</v>
+        <v>0.0002903318521093825</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8309088546704713</v>
+        <v>0.6496154310306327</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001435365364654158</v>
+        <v>0.0001109949631055014</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8308222975942267</v>
+        <v>0.6495465981026988</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.574128984836033e-05</v>
+        <v>5.856229200828367e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8308306512515021</v>
+        <v>0.6495520729055972</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.509169298536786e-05</v>
+        <v>2.605694527035538e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8308244287618962</v>
+        <v>0.6495461179355124</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.364889654592446e-05</v>
+        <v>9.919117236739567e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8308171216511042</v>
+        <v>0.6495392977543811</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>1.456405945771008e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8308095182872405</v>
+        <v>0.6495322729158204</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.106181251314092e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8308036475609364</v>
+        <v>0.6495265956842505</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8307977827649352</v>
+        <v>0.6495209231739664</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.830792103588227</v>
+        <v>0.6495153795058639</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.303898596494605</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8307872222899776</v>
+        <v>0.6495104583521425</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8307823010884298</v>
+        <v>0.6495104982076148</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.303898596494605</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8307822931173353</v>
+        <v>0.6495104902365203</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8307824525392244</v>
+        <v>0.6495106496584094</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.303898596494605</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.6495105540052759</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8307827076142472</v>
+        <v>0.6495109047334322</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8307824605103189</v>
+        <v>0.6495106576295039</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8307824206548466</v>
+        <v>0.6495106177740316</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.6495105540052759</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8307824286259411</v>
+        <v>0.6495106257451261</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683193</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.6495105540052759</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.02909442940683193</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8307824605103189</v>
+        <v>0.6495106576295039</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8307825561634525</v>
+        <v>0.6495107532826375</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.5106925914798269</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8307824923946967</v>
+        <v>0.6495106895138817</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8307824525392244</v>
+        <v>0.6495106496584094</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8307824286259411</v>
+        <v>0.6495106257451261</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683193</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8307821815220129</v>
+        <v>0.6495103786411979</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.303898596494605</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8307821018110682</v>
+        <v>0.6495102989302531</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.303898596494605</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8307821496376349</v>
+        <v>0.6495103467568198</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.830782269204052</v>
+        <v>0.6495104663232369</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.303898596494605</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8307822532618631</v>
+        <v>0.649510450381048</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.830782269204052</v>
+        <v>0.6495104663232369</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.303898596494605</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8307822532618631</v>
+        <v>0.649510450381048</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8307823090595242</v>
+        <v>0.6495105061787092</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683193</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8307823090595242</v>
+        <v>0.6495105061787092</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.02909442940683193</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8307823090595242</v>
+        <v>0.6495105061787092</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.6525037326661629</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8307824605103189</v>
+        <v>0.6495106576295039</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.02909442940683189</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8307826757298694</v>
+        <v>0.6495108728490544</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8307825880478303</v>
+        <v>0.6495107851670154</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.303898596494605</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8307825402212636</v>
+        <v>0.6495107373404486</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.1709055705931681</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8307825880478303</v>
+        <v>0.6495107851670154</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8307824047126576</v>
+        <v>0.6495106018318427</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683193</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8307824126837521</v>
+        <v>0.6495106098029372</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.02909442940683196</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8307824206548466</v>
+        <v>0.6495106177740316</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683196</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8307824286259411</v>
+        <v>0.6495106257451261</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.02909442940683193</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8307824286259411</v>
+        <v>0.6495106257451261</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.703898596494605</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8307824684814133</v>
+        <v>0.6495106656005983</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8307825322501692</v>
+        <v>0.6495107293693542</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.303898596494605</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8307826438454916</v>
+        <v>0.6495108409646766</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931682</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8307826916720583</v>
+        <v>0.6495108887912433</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.1709055705931682</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8307826518165861</v>
+        <v>0.649510848935771</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.02909442940683186</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8307825800767359</v>
+        <v>0.649510777195921</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683186</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8307826996431528</v>
+        <v>0.6495108967623378</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8307825402212636</v>
+        <v>0.6495107373404486</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8307823090595242</v>
+        <v>0.6495105061787092</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8307822612329575</v>
+        <v>0.6495104583521425</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8307822931173353</v>
+        <v>0.6495104902365203</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.6495105540052759</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.6495105540052759</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8307822771751464</v>
+        <v>0.6495104742943314</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.1709055705931682</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8307821576087293</v>
+        <v>0.6495103547279143</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.303898596494605</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8307821177532571</v>
+        <v>0.649510314872442</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661632</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8307822612329575</v>
+        <v>0.6495104583521425</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931682</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8307823967415632</v>
+        <v>0.6495105938607483</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.5106925914798269</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8307823807993743</v>
+        <v>0.6495105779185593</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.6495105540052759</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8307823170306187</v>
+        <v>0.6495105141498037</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683179</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8307822134063907</v>
+        <v>0.6495104105255758</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.02909442940683182</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8307820938399737</v>
+        <v>0.6495102909591587</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.852503732666163</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8307822134063907</v>
+        <v>0.6495104105255758</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.303898596494605</v>
+        <v>0.1709055705931682</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8307822612329575</v>
+        <v>0.6495104583521425</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931682</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8307823568860909</v>
+        <v>0.6495105540052759</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931682</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8307822373196742</v>
+        <v>0.6495104344388591</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.303898596494605</v>
+        <v>0.5117046516296658</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8307822452907686</v>
+        <v>0.6495104424099536</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000001.xlsx
+++ b/out/MLP-mamba2_repeat_1_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.1984095275402069</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.3117046516296653</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.7973228096961975</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.02909442940683214</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3016988635063171</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.1709055705931679</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.1897280514240265</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.255525141954422</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.298628181219101</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.2798832356929779</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3839943408966064</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.02909442940683214</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.5824334025382996</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.02909442940683214</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2939701974391937</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.1709055705931679</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.2757085263729095</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5106925914798269</v>
+        <v>0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3096072673797607</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.170905570593168</v>
+        <v>0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.6277866959571838</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.6800825595855713</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.534101894739158</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.7603594660758972</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.534101894739158</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.6191179156303406</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4234615564346313</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.5474475026130676</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5994338393211365</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8525037326661629</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3665773570537567</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.029094429406832</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.2702305912971497</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.2535622715950012</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.1977880895137787</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.029094429406832</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5488661527633667</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.029094429406832</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3304552137851715</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.029094429406832</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3240793645381927</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3035867512226105</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3932525515556335</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4956883788108826</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.2460561990737915</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3536513149738312</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.1320575922727585</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4417445063591003</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.3303356170654297</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4342703819274902</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4470075368881226</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.170905570593168</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5828626155853271</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.7280443906784058</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.534101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.9097037315368652</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.534101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.7994038462638855</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.534101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.9682327508926392</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.534101894739158</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.861596941947937</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.534101894739158</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002252983685754007</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09700682914012623</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9648436307907104</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.534101894739158</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1942727588303261</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3747886833462462</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.8645255565643311</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.8525037326661629</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8470928104491264</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1152870999546297</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.01449258998036385</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.029094429406832</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7024032384782659</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02339261016103038</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.4391595423221588</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.633720397376849</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02025939782276486</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.01750500500202179</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.02909442940683193</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.650820308430311</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009904359801443241</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.6531975269317627</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.02909442940683196</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.650343497418331</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004724318663416763</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.2529898583889008</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6525037326661629</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6498772306750361</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001965197408560933</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.6224045753479004</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.02909442940683196</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.649077877160457</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00136008686585621</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.2531222403049469</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.852503732666163</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6498318420035015</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005651940159429698</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.7783295512199402</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.02909442940683196</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6495998867178759</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002903318521093825</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3695845305919647</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1709055705931681</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6496154310306327</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001109949631055014</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.2452252954244614</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6495465981026988</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.856229200828367e-05</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.3808103501796722</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6495520729055972</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.605694527035538e-05</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.1798061728477478</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6495461179355124</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.919117236739567e-06</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3570597767829895</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6495392977543811</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.2880555093288422</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6495322729158204</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3239703178405762</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6495265956842505</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.2096247225999832</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6495209231739664</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4618445932865143</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.1709055705931681</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6495153795058639</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.5825990438461304</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1709055705931681</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6495104583521425</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3519681692123413</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.852503732666163</v>
+        <v>0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6495104982076148</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.7746171355247498</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1709055705931681</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6495104902365203</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.2630544900894165</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.852503732666163</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6495106496584094</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.9250267744064331</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.1709055705931681</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6495105540052759</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.2176646441221237</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.1709055705931681</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6495109047334322</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.2193241864442825</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6495106576295039</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4273604154586792</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6495106177740316</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4455048143863678</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6495105540052759</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3419252932071686</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6495106257451261</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2967772483825684</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.02909442940683193</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6495105540052759</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.9784830808639526</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.02909442940683193</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6495106576295039</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.2172495722770691</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.1709055705931681</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6495107532826375</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.2329282760620117</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5106925914798269</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6495106895138817</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2164808809757233</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6495106496584094</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.1437115967273712</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6495106257451261</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2387472540140152</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.02909442940683193</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6495103786411979</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5101129412651062</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.852503732666163</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6495102989302531</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5783815979957581</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.852503732666163</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6495103467568198</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.2832558453083038</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.852503732666163</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6495104663232369</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5222169756889343</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.1709055705931681</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.649510450381048</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.3929415047168732</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.852503732666163</v>
+        <v>0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6495104663232369</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5932173132896423</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1709055705931681</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.649510450381048</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3753321170806885</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.1709055705931681</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6495105061787092</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3211426734924316</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.02909442940683193</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6495105061787092</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.8540410995483398</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.02909442940683193</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6495105061787092</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3561426401138306</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6525037326661629</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6495106576295039</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.8336115479469299</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.02909442940683189</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6495108728490544</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.2060782015323639</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.852503732666163</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6495107851670154</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.591055154800415</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.1709055705931681</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6495107373404486</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.1374192535877228</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1709055705931681</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6495107851670154</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3560818731784821</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6495106018318427</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.324425995349884</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.02909442940683193</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6495106098029372</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.6161086559295654</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.02909442940683196</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6495106177740316</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2679310142993927</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.02909442940683196</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6495106257451261</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4270088672637939</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.02909442940683193</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6495106257451261</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.7605997920036316</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.852503732666163</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6495106656005983</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.6028876900672913</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.534101894739158</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6495107293693542</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.586073637008667</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.852503732666163</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6495108409646766</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.2538186013698578</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1709055705931682</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6495108887912433</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3592052459716797</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.1709055705931682</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.649510848935771</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.61617112159729</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.02909442940683186</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.649510777195921</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.1956071406602859</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.02909442940683186</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6495108967623378</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.2020846456289291</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6495107373404486</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.278589129447937</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6495105061787092</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4417054355144501</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6495104583521425</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4308430850505829</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6495104902365203</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4387757480144501</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6495105540052759</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.1991240680217743</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6495105540052759</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2532303929328918</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6495104742943314</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2491428852081299</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.1709055705931682</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6495103547279143</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.6792681217193604</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.852503732666163</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.649510314872442</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.6269600987434387</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8525037326661632</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6495104583521425</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4776350557804108</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1709055705931682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6495105938607483</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2043623775243759</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5106925914798269</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6495105779185593</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.3244921565055847</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6495105540052759</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.2544197738170624</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6495105141498037</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.1761271059513092</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.02909442940683179</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6495104105255758</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.777569055557251</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.02909442940683182</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6495102909591587</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.377991795539856</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.852503732666163</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6495104105255758</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.6420119404792786</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.1709055705931682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6495104583521425</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.2011166960000992</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1709055705931682</v>
+        <v>0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6495105540052759</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4239777326583862</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.1709055705931682</v>
+        <v>0.4400000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6495104344388591</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.5105313658714294</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5117046516296658</v>
+        <v>0.5800000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6495104424099536</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000001.xlsx
+++ b/out/MLP-mamba2_repeat_1_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.1984095275402069</v>
+        <v>0.1984093934297562</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.4399999999999999</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.7973228096961975</v>
+        <v>0.7973227500915527</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.58</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.3016988635063171</v>
+        <v>0.30169877409935</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.1897280514240265</v>
+        <v>0.1897279620170593</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.255525141954422</v>
+        <v>0.2555249929428101</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.298628181219101</v>
+        <v>0.2986282110214233</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.2798832356929779</v>
+        <v>0.2798830270767212</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.3839943408966064</v>
+        <v>0.383994072675705</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.5824334025382996</v>
+        <v>0.5824331641197205</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2939701974391937</v>
+        <v>0.2939700484275818</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.1199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.2757085263729095</v>
+        <v>0.2757083773612976</v>
       </c>
       <c r="JB12" t="n">
         <v>0.16</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.3096072673797607</v>
+        <v>0.309607058763504</v>
       </c>
       <c r="JB13" t="n">
         <v>0.16</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.6277866959571838</v>
+        <v>0.6277864575386047</v>
       </c>
       <c r="JB14" t="n">
         <v>0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.6800825595855713</v>
+        <v>0.6800826191902161</v>
       </c>
       <c r="JB15" t="n">
         <v>0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4234615564346313</v>
+        <v>0.4234614074230194</v>
       </c>
       <c r="JB18" t="n">
         <v>0.5799999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.5994338393211365</v>
+        <v>0.599433958530426</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.5799999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.3665773570537567</v>
+        <v>0.3665772974491119</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.2702305912971497</v>
+        <v>0.2702305614948273</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.8599999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.2535622715950012</v>
+        <v>0.2535621821880341</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.3304552137851715</v>
+        <v>0.3304550051689148</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.8599999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.3240793645381927</v>
+        <v>0.3240791261196136</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.3035867512226105</v>
+        <v>0.3035865724086761</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.8599999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.3932525515556335</v>
+        <v>0.3932523131370544</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.8599999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.4956883788108826</v>
+        <v>0.4956881701946259</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.8599999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.3536513149738312</v>
+        <v>0.3536509871482849</v>
       </c>
       <c r="JB32" t="n">
         <v>0.02000000000000007</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.1320575922727585</v>
+        <v>0.1320574134588242</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.1199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4417445063591003</v>
+        <v>0.4417442381381989</v>
       </c>
       <c r="JB34" t="n">
         <v>0.1600000000000001</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.3303356170654297</v>
+        <v>0.3303353488445282</v>
       </c>
       <c r="JB35" t="n">
         <v>0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.4342703819274902</v>
+        <v>0.4342701137065887</v>
       </c>
       <c r="JB36" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.4470075368881226</v>
+        <v>0.4470072686672211</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.5828626155853271</v>
+        <v>0.582862377166748</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.7280443906784058</v>
+        <v>0.7280441522598267</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.8645255565643311</v>
+        <v>0.8645256161689758</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.3</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01750500500202179</v>
+        <v>0.01750499755144119</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.8599999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.6224045753479004</v>
+        <v>0.6224044561386108</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.3</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.7783295512199402</v>
+        <v>0.778329610824585</v>
       </c>
       <c r="JB53" t="n">
         <v>0.1600000000000001</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.3695845305919647</v>
+        <v>0.3695845007896423</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.1199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.3808103501796722</v>
+        <v>0.3808102905750275</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.1798061728477478</v>
+        <v>0.1798065453767776</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.3570597767829895</v>
+        <v>0.3570597171783447</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.2880555093288422</v>
+        <v>0.2880554795265198</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.3239703178405762</v>
+        <v>0.3239702582359314</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.2176646441221237</v>
+        <v>0.2176645994186401</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.2193241864442825</v>
+        <v>0.219324141740799</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.7199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.4273604154586792</v>
+        <v>0.427360326051712</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.2172495722770691</v>
+        <v>0.2172491550445557</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.2329282760620117</v>
+        <v>0.2329283803701401</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.1199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.2164808809757233</v>
+        <v>0.2164811939001083</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.1437115967273712</v>
+        <v>0.1437114477157593</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.7199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.2387472540140152</v>
+        <v>0.2387472689151764</v>
       </c>
       <c r="JB79" t="n">
         <v>0.16</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.5101129412651062</v>
+        <v>0.5101132392883301</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1600000000000001</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.5783815979957581</v>
+        <v>0.5783818364143372</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.2832558453083038</v>
+        <v>0.2832559943199158</v>
       </c>
       <c r="JB82" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.5222169756889343</v>
+        <v>0.5222172737121582</v>
       </c>
       <c r="JB83" t="n">
         <v>0.5799999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.3929415047168732</v>
+        <v>0.392941802740097</v>
       </c>
       <c r="JB84" t="n">
         <v>0.3</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.5932173132896423</v>
+        <v>0.5932171940803528</v>
       </c>
       <c r="JB85" t="n">
         <v>0.3</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.3753321170806885</v>
+        <v>0.3753325045108795</v>
       </c>
       <c r="JB86" t="n">
         <v>0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3211426734924316</v>
+        <v>0.3211430013179779</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.8540410995483398</v>
+        <v>0.8540410399436951</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.3561426401138306</v>
+        <v>0.356143057346344</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.2060782015323639</v>
+        <v>0.2060786485671997</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.591055154800415</v>
+        <v>0.5910550355911255</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3560818731784821</v>
+        <v>0.3560822904109955</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.324425995349884</v>
+        <v>0.3244263231754303</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.6161086559295654</v>
+        <v>0.6161085963249207</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.2679310142993927</v>
+        <v>0.2679314315319061</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.1600000000000001</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.4270088672637939</v>
+        <v>0.4270093441009521</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.7605997920036316</v>
+        <v>0.7605997323989868</v>
       </c>
       <c r="JB99" t="n">
         <v>0.5799999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.6028876900672913</v>
+        <v>0.6028875708580017</v>
       </c>
       <c r="JB100" t="n">
         <v>0.5799999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.586073637008667</v>
+        <v>0.5860733389854431</v>
       </c>
       <c r="JB101" t="n">
         <v>0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.2538186013698578</v>
+        <v>0.253819078207016</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.3592052459716797</v>
+        <v>0.3592051565647125</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.61617112159729</v>
+        <v>0.6161710619926453</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.1956071406602859</v>
+        <v>0.1956070959568024</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.8599999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.2020846456289291</v>
+        <v>0.2020846009254456</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.4417054355144501</v>
+        <v>0.4417053461074829</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.4308430850505829</v>
+        <v>0.4308435320854187</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.1991240680217743</v>
+        <v>0.1991243362426758</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.2532303929328918</v>
+        <v>0.2532306909561157</v>
       </c>
       <c r="JB112" t="n">
         <v>0.02000000000000007</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.2491428852081299</v>
+        <v>0.2491431534290314</v>
       </c>
       <c r="JB113" t="n">
         <v>0.16</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.6792681217193604</v>
+        <v>0.6792684197425842</v>
       </c>
       <c r="JB114" t="n">
         <v>0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.6269600987434387</v>
+        <v>0.6269600391387939</v>
       </c>
       <c r="JB115" t="n">
         <v>0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4776350557804108</v>
+        <v>0.477635532617569</v>
       </c>
       <c r="JB116" t="n">
         <v>0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.2043623775243759</v>
+        <v>0.204362690448761</v>
       </c>
       <c r="JB117" t="n">
         <v>0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.3244921565055847</v>
+        <v>0.3244924545288086</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.1199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.2544197738170624</v>
+        <v>0.2544201016426086</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.377991795539856</v>
+        <v>0.377992182970047</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.6420119404792786</v>
+        <v>0.6420118808746338</v>
       </c>
       <c r="JB123" t="n">
         <v>0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.2011166960000992</v>
+        <v>0.2011169642210007</v>
       </c>
       <c r="JB124" t="n">
         <v>0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4239777326583862</v>
+        <v>0.4239780604839325</v>
       </c>
       <c r="JB125" t="n">
         <v>0.4400000000000002</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.5105313658714294</v>
+        <v>0.5105313062667847</v>
       </c>
       <c r="JB126" t="n">
         <v>0.5800000000000003</v>
